--- a/test-scenario-document.xlsx
+++ b/test-scenario-document.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\308345\Documents\Testing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{234E874B-EB96-495A-83DB-3C67A7152E2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2631A5C4-7EA4-4831-92F3-503FDD48D533}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{67B174C0-A3F8-404A-8057-880177842696}"/>
   </bookViews>
@@ -94,7 +94,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -106,6 +106,7 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -114,6 +115,12 @@
       <name val="Aptos Display"/>
       <family val="2"/>
       <scheme val="major"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -142,7 +149,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -161,6 +168,12 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -215,8 +228,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{471AC98E-F7DC-41E9-BE01-E4848EABEAA8}" name="Table2" displayName="Table2" ref="A1:F3" totalsRowShown="0" headerRowDxfId="3">
-  <autoFilter ref="A1:F3" xr:uid="{471AC98E-F7DC-41E9-BE01-E4848EABEAA8}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{471AC98E-F7DC-41E9-BE01-E4848EABEAA8}" name="Table2" displayName="Table2" ref="A1:F4" totalsRowShown="0" headerRowDxfId="3">
+  <autoFilter ref="A1:F4" xr:uid="{471AC98E-F7DC-41E9-BE01-E4848EABEAA8}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{3C3E9E5C-66AB-4D09-A42A-FD460C391976}" name="TestScenarioID"/>
     <tableColumn id="2" xr3:uid="{760841C4-B4ED-43CD-A664-4C039E1927A1}" name="Requirement ID"/>
@@ -546,7 +559,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4498443-BBA0-405C-925A-D66E72C899F6}">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21" customWidth="1"/>
@@ -617,7 +630,16 @@
         <v>14</v>
       </c>
     </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="7"/>
+      <c r="B4" s="7"/>
+      <c r="C4" s="7"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="7"/>
+      <c r="F4" s="8"/>
+    </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
   <tableParts count="1">
